--- a/tests/fixtures/hyou-no-soto-soto-sample.xlsx
+++ b/tests/fixtures/hyou-no-soto-soto-sample.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zeroa\AppData\Local\Temp\claude\C--WINDOWS-System32-WindowsPowerShell-v1-0\5b4e50e6-20a1-4af5-8ffb-8b6d6ca3f52b\scratchpad\mihon\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zeroa\AppData\Local\Temp\exally-mihon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{19FFE10D-4F51-406E-AABC-D211E27B254B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2822EB3A-DB23-4E46-8E3E-B6D66A5173A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21323" windowHeight="11107" xr2:uid="{45A4B0FC-7B0C-4FC7-A664-F11E6D39CFBB}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="11625" xr2:uid="{4B2DFCE6-2737-443B-8F5B-121A649A21C2}"/>
   </bookViews>
   <sheets>
     <sheet name="計算" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
     <t>数</t>
   </si>
   <si>
-    <t>正岡ｈ</t>
+    <t>標本七ｈ</t>
   </si>
 </sst>
 </file>
@@ -115,12 +115,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16E59687-7FF3-4041-8E5B-EDFB6BA0DF84}" name="R8.8" displayName="R8.8" ref="A1:C5" totalsRowShown="0">
-  <autoFilter ref="A1:C5" xr:uid="{16E59687-7FF3-4041-8E5B-EDFB6BA0DF84}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C5BAB066-FA36-4522-AF42-0AD5E9991A92}" name="R8.8" displayName="R8.8" ref="A1:C5" totalsRowShown="0">
+  <autoFilter ref="A1:C5" xr:uid="{C5BAB066-FA36-4522-AF42-0AD5E9991A92}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{25401FD3-7A6E-44F5-8EBF-5718B60081BC}" name="日付"/>
-    <tableColumn id="2" xr3:uid="{D4E908F6-078F-4077-A241-4F752D158513}" name="数"/>
-    <tableColumn id="3" xr3:uid="{EAA28E1B-83E2-4C59-9EBB-02729DCC8D1C}" name="正岡ｈ"/>
+    <tableColumn id="1" xr3:uid="{D40D9584-78DD-462A-A629-2270E2F3F690}" name="日付"/>
+    <tableColumn id="2" xr3:uid="{0C4B4BFD-1BF8-49F9-B7CE-CA7FDE522B25}" name="数"/>
+    <tableColumn id="3" xr3:uid="{78ABA204-C289-4310-BABF-E3033D33C7DB}" name="標本七ｈ"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -442,9 +442,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94B9B164-32A3-4DE6-8BA8-37B22AB9C605}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E0AC4D4-9431-4EC2-BDFE-6213DEDAD043}">
   <dimension ref="A1:C20"/>
   <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
+  <cols>
+    <col min="3" max="3" width="9.6875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A1" t="s">
@@ -503,7 +506,7 @@
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.7">
       <c r="B20">
-        <f>IFERROR(R8.8[[#This Row],[正岡ｈ]]*2, 0)</f>
+        <f>IFERROR(R8.8[[#This Row],[標本七ｈ]]*2, 0)</f>
         <v>0</v>
       </c>
     </row>

--- a/tests/fixtures/hyou-no-soto-soto-sample.xlsx
+++ b/tests/fixtures/hyou-no-soto-soto-sample.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zeroa\AppData\Local\Temp\exally-mihon\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url=""/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{2822EB3A-DB23-4E46-8E3E-B6D66A5173A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
